--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -62871,7 +62871,7 @@
         <v>1444</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.810000002384186</v>
+        <v>0.837999999523163</v>
       </c>
       <c r="D2718" t="n">
         <v>0.805999994277954</v>
@@ -62883,6 +62883,29 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>21850</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.824000000953674</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.837999999523163</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>11044</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.822000026702881</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.828000009059906</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.84799998998642</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>13145</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.867999970912933</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.824000000953674</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.857999980449677</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>929</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.837999999523163</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.832000017166138</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.833999991416931</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.837999999523163</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -62796,19 +62796,19 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>52</v>
+        <v>2335</v>
       </c>
       <c r="C2715" t="n">
-        <v>0.814000010490417</v>
+        <v>0.829999983310699</v>
       </c>
       <c r="D2715" t="n">
         <v>0.814000010490417</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.814000010490417</v>
+        <v>0.829999983310699</v>
       </c>
       <c r="F2715" t="n">
         <v>0.814000010490417</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>14317</v>
+        <v>52</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.846000015735626</v>
+        <v>0.814000010490417</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.800000011920929</v>
+        <v>0.814000010490417</v>
       </c>
       <c r="E2716" t="n">
-        <v>0.832000017166138</v>
+        <v>0.814000010490417</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.818000018596649</v>
+        <v>0.814000010490417</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>4657</v>
+        <v>14317</v>
       </c>
       <c r="C2717" t="n">
-        <v>0.825999975204468</v>
+        <v>0.846000015735626</v>
       </c>
       <c r="D2717" t="n">
-        <v>0.804000020027161</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="E2717" t="n">
+        <v>0.832000017166138</v>
+      </c>
+      <c r="F2717" t="n">
         <v>0.818000018596649</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>0.825999975204468</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>1444</v>
+        <v>4657</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.837999999523163</v>
+        <v>0.825999975204468</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.805999994277954</v>
+        <v>0.804000020027161</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.810000002384186</v>
+        <v>0.818000018596649</v>
       </c>
       <c r="F2718" t="n">
-        <v>0.837999999523163</v>
+        <v>0.825999975204468</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>21850</v>
+        <v>1444</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.850000023841858</v>
+        <v>0.837999999523163</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.824000000953674</v>
+        <v>0.805999994277954</v>
       </c>
       <c r="E2719" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="F2719" t="n">
         <v>0.837999999523163</v>
-      </c>
-      <c r="F2719" t="n">
-        <v>0.850000023841858</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>11044</v>
+        <v>21850</v>
       </c>
       <c r="C2720" t="n">
         <v>0.850000023841858</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.822000026702881</v>
+        <v>0.824000000953674</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.828000009059906</v>
+        <v>0.837999999523163</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.84799998998642</v>
+        <v>0.850000023841858</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>13145</v>
+        <v>11044</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.867999970912933</v>
+        <v>0.850000023841858</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.824000000953674</v>
+        <v>0.822000026702881</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.850000023841858</v>
+        <v>0.828000009059906</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.857999980449677</v>
+        <v>0.84799998998642</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>929</v>
+        <v>13145</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.837999999523163</v>
+        <v>0.867999970912933</v>
       </c>
       <c r="D2722" t="n">
+        <v>0.824000000953674</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.857999980449677</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>8086</v>
+      </c>
+      <c r="C2723" t="n">
         <v>0.832000017166138</v>
       </c>
-      <c r="E2722" t="n">
-        <v>0.833999991416931</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>0.837999999523163</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="D2723" t="n">
+        <v>0.824000000953674</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.832000017166138</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -71225,6 +71225,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>15283</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>0.857999980449677</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>0.836000025272369</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>0.857999980449677</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -71233,7 +71233,7 @@
         <v>15283</v>
       </c>
       <c r="C2726" t="n">
-        <v>0.857999980449677</v>
+        <v>0.860000014305115</v>
       </c>
       <c r="D2726" t="n">
         <v>0.836000025272369</v>
@@ -71248,6 +71248,32 @@
         <v>0.860000014305115</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>43298</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>0.819999992847443</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>0.842000007629395</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -71277,6 +71277,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>675</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>0.833999991416931</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>0.833999991416931</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -71303,6 +71303,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>28284</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>0.836000025272369</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>0.818000018596649</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>0.836000025272369</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>0.822000026702881</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>0.822000026702881</v>
+      </c>
+      <c r="H2729" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -71381,6 +71381,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>434</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>0.815999984741211</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>0.815999984741211</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>0.815999984741211</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>0.815999984741211</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>0.815999984741211</v>
+      </c>
+      <c r="H2732" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.818000018596649</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.804000020027161</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>8302</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.828000009059906</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.801999986171722</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.824000000953674</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.824000000953674</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.822000026702881</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>5600</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.808000028133392</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.822000026702881</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>0.822000026702881</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.808000028133392</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>7452</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.804000020027161</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.804000020027161</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -63339,7 +63339,9 @@
       <c r="E2738" t="n">
         <v>0.804000020027161</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.794000029563904</v>
+      </c>
       <c r="G2738" t="s">
         <v>7</v>
       </c>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -79954,6 +79954,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.776000022888184</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.762000024318695</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.791999995708466</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.791999995708466</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>8309</v>
+      </c>
+      <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -80012,6 +80012,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.787999987602234</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.787999987602234</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.763999998569489</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>12292</v>
+      </c>
+      <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -80041,6 +80041,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.762000024318695</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.776000022888184</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.776000022888184</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>7184</v>
+      </c>
+      <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -80070,6 +80070,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.762000024318695</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.773999989032745</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.773999989032745</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>198</v>
+      </c>
+      <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -80078,13 +80078,13 @@
         <v>46318.2916666667</v>
       </c>
       <c r="C2749" t="n">
-        <v>0.790000021457672</v>
+        <v>0.773999989032745</v>
       </c>
       <c r="D2749" t="n">
-        <v>0.790000021457672</v>
+        <v>0.773999989032745</v>
       </c>
       <c r="E2749" t="n">
-        <v>0.762000024318695</v>
+        <v>0.773999989032745</v>
       </c>
       <c r="F2749" t="n">
         <v>0.773999989032745</v>
@@ -80096,6 +80096,35 @@
         <v>198</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.773999989032745</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.773999989032745</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.773999989032745</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>168</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -80107,13 +80107,13 @@
         <v>46321.3333333333</v>
       </c>
       <c r="C2750" t="n">
-        <v>0.773999989032745</v>
+        <v>0.769999980926514</v>
       </c>
       <c r="D2750" t="n">
-        <v>0.773999989032745</v>
+        <v>0.769999980926514</v>
       </c>
       <c r="E2750" t="n">
-        <v>0.773999989032745</v>
+        <v>0.769999980926514</v>
       </c>
       <c r="F2750" t="n">
         <v>0.769999980926514</v>
@@ -80125,6 +80125,35 @@
         <v>168</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.773999989032745</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.783999979496002</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.763999998569489</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.783999979496002</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.783999979496002</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>6185</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -80136,7 +80136,7 @@
         <v>46322.3333333333</v>
       </c>
       <c r="C2751" t="n">
-        <v>0.773999989032745</v>
+        <v>0.769999980926514</v>
       </c>
       <c r="D2751" t="n">
         <v>0.783999979496002</v>
@@ -80154,6 +80154,35 @@
         <v>6185</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>0.765999972820282</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>0.765999972820282</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0.765999972820282</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>0.78600001335144</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>0.78600001335144</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>473</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CLF.MI.xlsx
+++ b/data/CLF.MI.xlsx
@@ -80168,7 +80168,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="D2752" t="n">
-        <v>0.765999972820282</v>
+        <v>0.78600001335144</v>
       </c>
       <c r="E2752" t="n">
         <v>0.765999972820282</v>
@@ -80183,6 +80183,35 @@
         <v>473</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>0.782000005245209</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>0.782000005245209</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>0.76800000667572</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>0.76800000667572</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>0.76800000667572</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>1090</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>
